--- a/SOLD_ALBA.xlsx
+++ b/SOLD_ALBA.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1987,6 +1987,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="30.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -2162,7 +2165,7 @@
         <v>265</v>
       </c>
       <c r="E9">
-        <v>1048.15</v>
+        <v>1048.1500000000001</v>
       </c>
       <c r="F9" t="s">
         <v>356</v>
@@ -2182,7 +2185,7 @@
         <v>260</v>
       </c>
       <c r="E10">
-        <v>75.56999999999999</v>
+        <v>75.569999999999993</v>
       </c>
       <c r="F10" t="s">
         <v>357</v>
@@ -2282,7 +2285,7 @@
         <v>269</v>
       </c>
       <c r="E15">
-        <v>1294.4</v>
+        <v>1294.4000000000001</v>
       </c>
       <c r="F15" t="s">
         <v>362</v>
@@ -2362,7 +2365,7 @@
         <v>268</v>
       </c>
       <c r="E19">
-        <v>1101.88</v>
+        <v>1101.8800000000001</v>
       </c>
       <c r="F19" t="s">
         <v>366</v>
@@ -2422,7 +2425,7 @@
         <v>275</v>
       </c>
       <c r="E22">
-        <v>279.4</v>
+        <v>279.39999999999998</v>
       </c>
       <c r="F22" t="s">
         <v>369</v>
@@ -2482,7 +2485,7 @@
         <v>278</v>
       </c>
       <c r="E25">
-        <v>615.0599999999999</v>
+        <v>615.05999999999995</v>
       </c>
       <c r="F25" t="s">
         <v>372</v>
@@ -2542,7 +2545,7 @@
         <v>281</v>
       </c>
       <c r="E28">
-        <v>65.04000000000001</v>
+        <v>65.040000000000006</v>
       </c>
       <c r="F28" t="s">
         <v>375</v>
@@ -2622,7 +2625,7 @@
         <v>268</v>
       </c>
       <c r="E32">
-        <v>326.66</v>
+        <v>326.66000000000003</v>
       </c>
       <c r="F32" t="s">
         <v>379</v>
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="E33">
-        <v>259.84</v>
+        <v>259.83999999999997</v>
       </c>
       <c r="F33" t="s">
         <v>380</v>
@@ -2742,7 +2745,7 @@
         <v>273</v>
       </c>
       <c r="E38">
-        <v>798.1799999999999</v>
+        <v>798.18</v>
       </c>
       <c r="F38" t="s">
         <v>385</v>
@@ -2982,7 +2985,7 @@
         <v>287</v>
       </c>
       <c r="E50">
-        <v>149.36</v>
+        <v>149.36000000000001</v>
       </c>
       <c r="F50" t="s">
         <v>397</v>
@@ -3022,7 +3025,7 @@
         <v>264</v>
       </c>
       <c r="E52">
-        <v>65.45999999999999</v>
+        <v>65.459999999999994</v>
       </c>
       <c r="F52" t="s">
         <v>399</v>
@@ -3142,7 +3145,7 @@
         <v>278</v>
       </c>
       <c r="E58">
-        <v>541.1900000000001</v>
+        <v>541.19000000000005</v>
       </c>
       <c r="F58" t="s">
         <v>405</v>
@@ -3202,7 +3205,7 @@
         <v>266</v>
       </c>
       <c r="E61">
-        <v>5017.98</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="F61" t="s">
         <v>408</v>
@@ -3222,7 +3225,7 @@
         <v>269</v>
       </c>
       <c r="E62">
-        <v>625.5700000000001</v>
+        <v>625.57000000000005</v>
       </c>
       <c r="F62" t="s">
         <v>409</v>
@@ -3682,7 +3685,7 @@
         <v>306</v>
       </c>
       <c r="E85">
-        <v>586.1799999999999</v>
+        <v>586.17999999999995</v>
       </c>
       <c r="F85" t="s">
         <v>432</v>
@@ -3762,7 +3765,7 @@
         <v>310</v>
       </c>
       <c r="E89">
-        <v>1046.41</v>
+        <v>1046.4100000000001</v>
       </c>
       <c r="F89" t="s">
         <v>436</v>
@@ -3822,7 +3825,7 @@
         <v>307</v>
       </c>
       <c r="E92">
-        <v>632.58</v>
+        <v>632.58000000000004</v>
       </c>
       <c r="F92" t="s">
         <v>439</v>
@@ -4082,7 +4085,7 @@
         <v>272</v>
       </c>
       <c r="E105">
-        <v>2520.78</v>
+        <v>2520.7800000000002</v>
       </c>
       <c r="F105" t="s">
         <v>452</v>
@@ -4462,7 +4465,7 @@
         <v>320</v>
       </c>
       <c r="E124">
-        <v>1051.14</v>
+        <v>1051.1400000000001</v>
       </c>
       <c r="F124" t="s">
         <v>469</v>
@@ -4782,7 +4785,7 @@
         <v>330</v>
       </c>
       <c r="E140">
-        <v>2373.43</v>
+        <v>2373.4299999999998</v>
       </c>
       <c r="F140" t="s">
         <v>484</v>
@@ -4862,7 +4865,7 @@
         <v>273</v>
       </c>
       <c r="E144">
-        <v>721.3200000000001</v>
+        <v>721.32</v>
       </c>
       <c r="F144" t="s">
         <v>488</v>
@@ -4882,7 +4885,7 @@
         <v>267</v>
       </c>
       <c r="E145">
-        <v>1065.88</v>
+        <v>1065.8800000000001</v>
       </c>
       <c r="F145" t="s">
         <v>489</v>
@@ -4942,7 +4945,7 @@
         <v>262</v>
       </c>
       <c r="E148">
-        <v>5017.98</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="F148" t="s">
         <v>408</v>
@@ -4962,7 +4965,7 @@
         <v>263</v>
       </c>
       <c r="E149">
-        <v>9692.129999999999</v>
+        <v>9692.1299999999992</v>
       </c>
       <c r="F149" t="s">
         <v>492</v>
@@ -5142,7 +5145,7 @@
         <v>293</v>
       </c>
       <c r="E158">
-        <v>535.8</v>
+        <v>535.79999999999995</v>
       </c>
       <c r="F158" t="s">
         <v>501</v>
@@ -5282,7 +5285,7 @@
         <v>339</v>
       </c>
       <c r="E165">
-        <v>310.65</v>
+        <v>310.64999999999998</v>
       </c>
       <c r="F165" t="s">
         <v>507</v>
@@ -5322,7 +5325,7 @@
         <v>340</v>
       </c>
       <c r="E167">
-        <v>656.4400000000001</v>
+        <v>656.44</v>
       </c>
       <c r="F167" t="s">
         <v>508</v>
@@ -5622,7 +5625,7 @@
         <v>312</v>
       </c>
       <c r="E182">
-        <v>269.09</v>
+        <v>269.08999999999997</v>
       </c>
       <c r="F182" t="s">
         <v>522</v>
@@ -5702,7 +5705,7 @@
         <v>326</v>
       </c>
       <c r="E186">
-        <v>137.36</v>
+        <v>137.36000000000001</v>
       </c>
       <c r="F186" t="s">
         <v>525</v>
@@ -5782,7 +5785,7 @@
         <v>283</v>
       </c>
       <c r="E190">
-        <v>70.06999999999999</v>
+        <v>70.069999999999993</v>
       </c>
       <c r="F190" t="s">
         <v>528</v>
@@ -5942,7 +5945,7 @@
         <v>267</v>
       </c>
       <c r="E198">
-        <v>1088.63</v>
+        <v>1088.6300000000001</v>
       </c>
       <c r="F198" t="s">
         <v>535</v>
@@ -5982,7 +5985,7 @@
         <v>280</v>
       </c>
       <c r="E200">
-        <v>69.81999999999999</v>
+        <v>69.819999999999993</v>
       </c>
       <c r="F200" t="s">
         <v>537</v>
